--- a/Front-End/src/Components/temp.xlsx
+++ b/Front-End/src/Components/temp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Soulayman\Desktop\Certificate-Medical\Front-End\src\Components\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5EC322E-CD10-40F2-9D44-5C0D94FB91BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0697AB33-C6D2-4493-A498-00EC3C9E5B77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2244" yWindow="7548" windowWidth="17280" windowHeight="8940" xr2:uid="{0339D642-AD52-43F8-9658-E000E99F9CF9}"/>
+    <workbookView xWindow="11520" yWindow="0" windowWidth="11520" windowHeight="12504" xr2:uid="{0339D642-AD52-43F8-9658-E000E99F9CF9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -483,18 +483,19 @@
   <dimension ref="A1:M1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="1"/>
-    <col min="2" max="3" width="25.21875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="14.88671875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" style="1"/>
-    <col min="6" max="6" width="14.6640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="14.44140625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="35.6640625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="26.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="27.77734375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.5546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10.88671875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="18.44140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="19" style="1" customWidth="1"/>
+    <col min="8" max="8" width="37.77734375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="31.77734375" style="1" customWidth="1"/>
     <col min="10" max="10" width="17.77734375" style="1" customWidth="1"/>
-    <col min="11" max="11" width="10.88671875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="12.77734375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="15.5546875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="25.33203125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="22.6640625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="33.5546875" style="1" customWidth="1"/>
     <col min="14" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
